--- a/output/full_scan/batch_seq7_2026-06-11.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1038.770642687578</v>
+        <v>1313.770642687579</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>286.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.78147778519806</v>
+        <v>66.78147773638966</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.24925363080652</v>
+        <v>25.24925361503156</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.877064268757854</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.2706450325411031</v>
+        <v>-0.2706450322548956</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>815</v>
+        <v>1055</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>43.3</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.71666773249828</v>
+        <v>63.71666756691094</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.50547355555871</v>
+        <v>20.50547357392884</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7.466474546853765</v>
+        <v>7.506909233347115</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2900179901442809</v>
+        <v>0.2900179902110626</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6690</v>
+        <v>6834</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>785.1272408645945</v>
+        <v>1013.698390288837</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>177</v>
+        <v>76.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>55.05672842340246</v>
+        <v>62.01728297808965</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.43854918822972</v>
+        <v>44.86580142995014</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.512724086459451</v>
+        <v>2.369839028883693</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.3114928094070901</v>
+        <v>-1.076693860638857</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6834</v>
+        <v>6579</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>773.5619813435601</v>
+        <v>975.7325348720824</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>76.5</v>
+        <v>163</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.01728298710885</v>
+        <v>57.72249178099449</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>44.8658015140264</v>
+        <v>39.07355402632539</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.35619813435601</v>
+        <v>0.5732534872082475</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-1.076693861106306</v>
+        <v>-1.922993060946386</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6670</v>
+        <v>6491</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>723.4770355176607</v>
+        <v>967.650983991351</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>282</v>
+        <v>323.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.51917892670161</v>
+        <v>62.06660815309242</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.31984688769137</v>
+        <v>36.37163631396339</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.8477035517660745</v>
+        <v>0.7650983991351075</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.627951919499875</v>
+        <v>-0.2847146659179458</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6811</v>
+        <v>6625</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>700.3475900295047</v>
+        <v>936.74450390885</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>227.5</v>
+        <v>77.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.11513396031848</v>
+        <v>69.25255056100372</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29.18110777304704</v>
+        <v>18.5176803644488</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.534759002950469</v>
+        <v>4.174450390884999</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.4818428112134238</v>
+        <v>0.5109485849433083</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6491</v>
+        <v>6670</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>677.5078635601825</v>
+        <v>933.580485595706</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>323.5</v>
+        <v>282</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.06660826682212</v>
+        <v>62.51917877202582</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.3716362536359</v>
+        <v>26.31984703206385</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.7507863560182555</v>
+        <v>0.8580485595706151</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.2847146664903661</v>
+        <v>1.627951921121666</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6579</v>
+        <v>6690</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>675.6289752842991</v>
+        <v>925.1272408645945</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.72249187963168</v>
+        <v>55.05672828962593</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>39.07355404248845</v>
+        <v>20.43854920115916</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5628975284299151</v>
+        <v>2.512724086459451</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-1.922993060946386</v>
+        <v>-0.3114928090255233</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6693</v>
+        <v>6585</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>661.7951837833675</v>
+        <v>885.7883350103168</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>155</v>
+        <v>124.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>52.65704957035776</v>
+        <v>79.80063924494459</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38.03589197661629</v>
+        <v>49.66709839970056</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.17951837833675</v>
+        <v>1.578833501031682</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.5058081561230523</v>
+        <v>3.017829376368421</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6651</v>
+        <v>6821</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>654.3221768484127</v>
+        <v>867.7191564431413</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>126</v>
+        <v>67.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46.6329276406866</v>
+        <v>58.61782603655235</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>36.28960365176768</v>
+        <v>26.9844105807686</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4322176848412715</v>
+        <v>0.2719156443141296</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-3.201488356096741</v>
+        <v>-0.2990757102655905</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6494</v>
+        <v>6517</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>654.0269397480898</v>
+        <v>860.9637068258752</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>56.5</v>
+        <v>69</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>53.68251045458876</v>
+        <v>61.81058683562213</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26.23986856924753</v>
+        <v>25.86999353053028</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.902693974808985</v>
+        <v>2.096370682587521</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.5798988425686019</v>
+        <v>0.6913921492745712</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6556</v>
+        <v>6757</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>652.1990127746118</v>
+        <v>831.7997058620405</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.07857427456091</v>
+        <v>55.82617190948575</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>39.86653445439491</v>
+        <v>24.36843018667884</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.2199012774611783</v>
+        <v>2.179970586204048</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0229651569380213</v>
+        <v>-0.2231199362256082</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6585</v>
+        <v>6642</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>645.6622639624127</v>
+        <v>809.9281890639447</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>124.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>79.80063940774941</v>
+        <v>56.26721420938446</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>49.66709831508874</v>
+        <v>50.93698160863964</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.566226396241268</v>
+        <v>0.4928189063944743</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.01782937627304</v>
+        <v>-1.176680836634101</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6642</v>
+        <v>6693</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>639.9281890639447</v>
+        <v>801.7951837833675</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>155</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.26721421837737</v>
+        <v>52.6570495294332</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>50.9369815917249</v>
+        <v>38.03589196521012</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4928189063944743</v>
+        <v>1.17951837833675</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.176680836653182</v>
+        <v>0.5058081564664771</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6792</v>
+        <v>6494</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>635.9765437130054</v>
+        <v>794.0269397480898</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>65.2</v>
+        <v>56.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>48.15761918576723</v>
+        <v>53.68251042247464</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.80266089730698</v>
+        <v>26.23986860391318</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.597654371300543</v>
+        <v>1.902693974808985</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.7377557533406445</v>
+        <v>-0.5798988425972154</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6625</v>
+        <v>6556</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>635.8918169449171</v>
+        <v>792.1990127746118</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>77.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.25255081276617</v>
+        <v>57.07857472160779</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18.51768027459052</v>
+        <v>39.86653451898382</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.089181694491704</v>
+        <v>0.2199012774611783</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.5109485845617184</v>
+        <v>0.0229651568044761</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6698</v>
+        <v>6592</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>614.6295240626071</v>
+        <v>774.3884510619012</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>37.75</v>
+        <v>66.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>52.45784290732512</v>
+        <v>69.53237940712432</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>38.30433399976073</v>
+        <v>27.96969023585682</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4629524062607088</v>
+        <v>0.9388451061901112</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1592047281698292</v>
+        <v>0.6734688224382981</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6605</v>
+        <v>6672</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>608.1561024267064</v>
+        <v>766.8869516976449</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>141</v>
+        <v>213.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.14067582182951</v>
+        <v>54.31166444999474</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.4892957515512</v>
+        <v>28.06885372348979</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.315610242670646</v>
+        <v>0.6886951697644927</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.6603055963839615</v>
+        <v>-0.6852624768346853</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6531</v>
+        <v>6792</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>606.8695918026492</v>
+        <v>766.0171208634911</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>890</v>
+        <v>65.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>44.00338187424953</v>
+        <v>48.15761915201825</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>27.32960463344537</v>
+        <v>38.80266090235179</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.686959180264923</v>
+        <v>0.6017120863491119</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-36.27671061171625</v>
+        <v>-0.7377557533406445</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6592</v>
+        <v>6606</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>604.2480649020841</v>
+        <v>764.7657957741454</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>66.8</v>
+        <v>25.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>69.5323795397811</v>
+        <v>55.82236155609646</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.96969023249566</v>
+        <v>22.53343338778089</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9248064902084172</v>
+        <v>0.4765795774145477</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6734688225336973</v>
+        <v>-0.0257917940517183</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6672</v>
+        <v>6598</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>601.7225220380165</v>
+        <v>753.8887639988994</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>213.5</v>
+        <v>24.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.31166446684904</v>
+        <v>54.89332296705872</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.06885375301978</v>
+        <v>29.74532599883463</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.672252203801643</v>
+        <v>0.8888763998899407</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.6852624769110047</v>
+        <v>-0.0325205635869213</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6716</v>
+        <v>6605</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>600.8909471723665</v>
+        <v>748.4038609282658</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>86.3</v>
+        <v>141</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>40.13088379123266</v>
+        <v>55.14067556295032</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>36.34701640997181</v>
+        <v>25.48929573156024</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5890947172366506</v>
+        <v>1.340386092826573</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-3.028529969859844</v>
+        <v>0.6603055967655509</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>589.4986067176135</v>
+        <v>729.6521148944806</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>95.3</v>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>64.81975943711262</v>
+        <v>64.81975930721197</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24.17093788455512</v>
+        <v>24.170937871543</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.949860671761348</v>
+        <v>0.9652114894480596</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.8587579280057906</v>
+        <v>0.8587579287689717</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6517</v>
+        <v>6719</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>585.9637068258752</v>
+        <v>723.1797624872876</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.81058698388101</v>
+        <v>46.25346927908045</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.86999351177273</v>
+        <v>46.71846333154649</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.096370682587521</v>
+        <v>0.3179762487287582</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6913921494081321</v>
+        <v>-5.821149467817991</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6606</v>
+        <v>6525</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>584.741958779083</v>
+        <v>714.5913841561824</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25.9</v>
+        <v>116.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.8223616214313</v>
+        <v>53.30739458275234</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.53343352797281</v>
+        <v>27.34231293517426</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4741958779082998</v>
+        <v>0.4591384156182344</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0257917940612579</v>
+        <v>-1.729737768516596</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6510</v>
+        <v>6684</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>568.5441391290524</v>
+        <v>712.3715765131551</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>3390</v>
+        <v>49.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>48.7819822692146</v>
+        <v>59.29327894085725</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.69971322014859</v>
+        <v>20.9079456748861</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8544139129052428</v>
+        <v>1.23715765131551</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>7.212995803726756</v>
+        <v>0.4734721183015166</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6719</v>
+        <v>6510</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>548.1147367760211</v>
+        <v>708.5441391290524</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>214</v>
+        <v>3390</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46.25346930437873</v>
+        <v>48.78198226610252</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46.71846328277175</v>
+        <v>20.69971322014858</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.311473677602111</v>
+        <v>0.8544139129052428</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-5.821149467913422</v>
+        <v>7.212995804681015</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6598</v>
+        <v>6763</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>543.8084446746509</v>
+        <v>704.2363563616452</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>24.5</v>
+        <v>48.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.89332318775283</v>
+        <v>57.82629051245566</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29.74532603548119</v>
+        <v>25.28214940573761</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.880844467465096</v>
+        <v>0.9236356361645236</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0325205636823201</v>
+        <v>0.5825125323242726</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6742</v>
+        <v>6811</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>543.3181975592452</v>
+        <v>700.3475900295047</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>54.6</v>
+        <v>227.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.9436801428219</v>
+        <v>55.11513385122603</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38.05915416966129</v>
+        <v>29.18110777445356</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8318197559245242</v>
+        <v>0.534759002950469</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.7598456693963129</v>
+        <v>-0.4818428109272297</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6525</v>
+        <v>6698</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>534.5263553360473</v>
+        <v>694.6690664924367</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>116.5</v>
+        <v>37.75</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>53.30739458989242</v>
+        <v>52.45784289465191</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.34231291937216</v>
+        <v>38.30433402570213</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4526355336047428</v>
+        <v>0.4669066492436711</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.729737768383037</v>
+        <v>-0.1592047282366073</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6538</v>
+        <v>6515</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>529.4958914003624</v>
+        <v>687.2671807033003</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>94.7</v>
+        <v>8720</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>42.10746474213092</v>
+        <v>48.15648552928975</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>41.61817953923138</v>
+        <v>29.37839361479441</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.449589140036245</v>
+        <v>1.226718070330028</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-4.632012935918517</v>
+        <v>-55.18519803052115</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6695</v>
+        <v>6531</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>523.6280913732032</v>
+        <v>667.0303624250606</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>49.55</v>
+        <v>890</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>44.65630934196157</v>
+        <v>44.00338187032973</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.50611048218996</v>
+        <v>27.32960461051644</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.362809137320322</v>
+        <v>0.703036242506056</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.293030408365025</v>
+        <v>-36.27671061219346</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6684</v>
+        <v>6668</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>512.3715765131551</v>
+        <v>661.0896030892486</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>49.4</v>
+        <v>38.25</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>59.2932790579095</v>
+        <v>50.53366315196172</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.90794568909109</v>
+        <v>27.01673382182258</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.23715765131551</v>
+        <v>0.6089603089248637</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.4734721182538189</v>
+        <v>-0.3422720101207107</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6757</v>
+        <v>6691</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>511.6733849713154</v>
+        <v>657.6222744100903</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>55.6</v>
+        <v>637</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.8261721202698</v>
+        <v>49.73465059686687</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.36843002488973</v>
+        <v>11.702348156277</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.167338497131543</v>
+        <v>1.262227441009029</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.2231199362256082</v>
+        <v>-1.304443644515623</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6570</v>
+        <v>6651</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>498.4351059834042</v>
+        <v>654.3221768484127</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>56.7</v>
+        <v>126</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.60506033991758</v>
+        <v>46.63292759798132</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>28.88955010297958</v>
+        <v>36.28960372466791</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8435105983404262</v>
+        <v>0.4322176848412715</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.5934098798537093</v>
+        <v>-3.201488355963173</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6807</v>
+        <v>6597</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>488.238803456451</v>
+        <v>641.672070395376</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>34.1</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>47.09877213238212</v>
+        <v>47.45674091038193</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.72188669451004</v>
+        <v>13.44814876437757</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3238803456451049</v>
+        <v>0.1672070395376003</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.289366765863801</v>
+        <v>-1.179804106982277</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6668</v>
+        <v>6570</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>481.0668400312167</v>
+        <v>638.4351059834042</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>38.25</v>
+        <v>56.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.53366322332827</v>
+        <v>58.60506028611103</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.01673382483431</v>
+        <v>28.88955010297958</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6066840031216649</v>
+        <v>0.8435105983404262</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.3422720101302557</v>
+        <v>-0.5934098799109506</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6799</v>
+        <v>6807</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>478.7992916798816</v>
+        <v>628.6242330990877</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>83.8</v>
+        <v>34.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>33.92468416728498</v>
+        <v>47.09877213238212</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>35.14584136586308</v>
+        <v>27.72188669629925</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3799291679881594</v>
+        <v>0.36242330990878</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-3.050840016655882</v>
+        <v>0.2893667654822146</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6743</v>
+        <v>6538</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>471.8457132793245</v>
+        <v>619.4958914003624</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>29.25</v>
+        <v>94.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.42513455323016</v>
+        <v>42.10746471412584</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.23174459575709</v>
+        <v>41.61817953525517</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.18457132793245</v>
+        <v>1.449589140036245</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1356780771590378</v>
+        <v>-4.632012935899445</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6658</v>
+        <v>6831</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>469.647743636658</v>
+        <v>609.7993864443771</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>175</v>
+        <v>719</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.45694544613018</v>
+        <v>53.4602735897108</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>43.39669109851353</v>
+        <v>30.97491835405729</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4647743636657993</v>
+        <v>0.9799386444377064</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-7.681879407245841</v>
+        <v>-14.8354387092622</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6546</v>
+        <v>6550</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>464.4100027652376</v>
+        <v>605.7400780428427</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>72.7</v>
+        <v>13.45</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45.5026727554875</v>
+        <v>33.66860289151374</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.48761122403119</v>
+        <v>36.81049218533345</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4410002765237625</v>
+        <v>0.574007804284267</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.10086921666676</v>
+        <v>0.0489145946776885</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6667</v>
+        <v>6716</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>460.2546921439063</v>
+        <v>600.8909471723665</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>263.5</v>
+        <v>86.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>48.12968790435647</v>
+        <v>40.13088376411105</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.87458377235366</v>
+        <v>36.34701640997181</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5254692143906324</v>
+        <v>0.5890947172366506</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.3424180074994698</v>
+        <v>-3.028529969802623</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6831</v>
+        <v>6581</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>459.3842932686708</v>
+        <v>599.5940575611705</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>719</v>
+        <v>109</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.46027358790334</v>
+        <v>52.25893329713213</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.9749183722018</v>
+        <v>13.32999916726637</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9384293268670814</v>
+        <v>0.4594057561170542</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-14.83543870933852</v>
+        <v>-0.0817194480657131</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6706</v>
+        <v>6781</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>458.8741225191882</v>
+        <v>594.2974229444692</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>161</v>
+        <v>1155</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>42.46024564965975</v>
+        <v>50.3934043122857</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.22121032329054</v>
+        <v>14.01546138421273</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3874122519188179</v>
+        <v>1.429742294446912</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-6.030018061355047</v>
+        <v>-10.47058926200971</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6770</v>
+        <v>6667</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>457.6949346584653</v>
+        <v>575.2546921439064</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>263.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>44.40644191746679</v>
+        <v>48.12968778711839</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.95629228133082</v>
+        <v>16.87458376051318</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2694934658465324</v>
+        <v>0.5254692143906324</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.978218731545731</v>
+        <v>-0.3424180074994698</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6669</v>
+        <v>6589</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>447.7214496106299</v>
+        <v>566.9572353556866</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>4900</v>
+        <v>43.85</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.37455754182099</v>
+        <v>46.36139833073048</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.9736195352945</v>
+        <v>24.04690212834809</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.272144961062985</v>
+        <v>0.6957235355686602</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-88.24703809885665</v>
+        <v>0.493252196864181</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6761</v>
+        <v>6743</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>444.9535633100718</v>
+        <v>556.9038174398327</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>196</v>
+        <v>29.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>44.55252293928905</v>
+        <v>51.42513446956651</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.80730702668246</v>
+        <v>25.23174464842129</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4953563310071801</v>
+        <v>1.190381743983273</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.015831649402444</v>
+        <v>-0.1356780771971967</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6573</v>
+        <v>6512</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>440.8351339511608</v>
+        <v>554.5611148040662</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14.9</v>
+        <v>19.55</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.50943553849228</v>
+        <v>51.97241860075693</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.83610659108213</v>
+        <v>6.002721175273721</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.58351339511608</v>
+        <v>0.9561114804066214</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0889901435052228</v>
+        <v>0.0933993633108999</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6526</v>
+        <v>6756</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>440.2515176183554</v>
+        <v>549.132076953759</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>618</v>
+        <v>92.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.74676158308032</v>
+        <v>45.93954178176789</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.00864394897137</v>
+        <v>32.35615299752278</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5251517618355358</v>
+        <v>0.4132076953758988</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-14.22951317631398</v>
+        <v>-1.818343579189686</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6581</v>
+        <v>6498</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>439.4168852615901</v>
+        <v>547.8936089886117</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>109</v>
+        <v>98.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.25893339312769</v>
+        <v>46.44517605790304</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.32999914073468</v>
+        <v>31.62694972192853</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.441688526159003</v>
+        <v>0.2893608988611701</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0817194480657131</v>
+        <v>-1.215764921547201</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6597</v>
+        <v>6788</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>436.672070395376</v>
+        <v>547.1276999830501</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>404.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>47.45674089614775</v>
+        <v>45.04279863438331</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.44814877534344</v>
+        <v>11.1240036570713</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1672070395376003</v>
+        <v>1.212769998305012</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.179804106505294</v>
+        <v>0.1164266642133387</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6550</v>
+        <v>6776</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>435.6946829269514</v>
+        <v>544.283994104377</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>13.45</v>
+        <v>59.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>33.66860253181393</v>
+        <v>50.87379043725076</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>36.81049208937126</v>
+        <v>11.823681023134</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5694682926951435</v>
+        <v>0.9283994104377056</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0489145951069747</v>
+        <v>0.09655028294871849</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6498</v>
+        <v>6614</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>432.8936089886117</v>
+        <v>534.3275032432559</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>98.3</v>
+        <v>40</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.44517611518662</v>
+        <v>49.46121298679018</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>31.62694969989602</v>
+        <v>11.86296651094448</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2893608988611701</v>
+        <v>0.9327503243255972</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.2157649216426</v>
+        <v>0.1419003922492032</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6763</v>
+        <v>6645</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>429.2363563616452</v>
+        <v>519.5461305181836</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>48.3</v>
+        <v>12.9</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>57.82629075538203</v>
+        <v>53.62649751418132</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.28214918946912</v>
+        <v>31.36262623925</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9236356361645236</v>
+        <v>0.4546130518183581</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5825125319808402</v>
+        <v>0.204988162391613</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6588</v>
+        <v>6742</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>424.1720564081944</v>
+        <v>513.4247704830204</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>54.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>32.42839817005775</v>
+        <v>50.94368008625673</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.8634700167452</v>
+        <v>38.05915417639847</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9172056408194332</v>
+        <v>0.8424770483020465</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-2.019198337192022</v>
+        <v>-0.7598456693486151</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6512</v>
+        <v>6790</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>414.5611148040662</v>
+        <v>502.979470782394</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>19.55</v>
+        <v>39.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.97241859801763</v>
+        <v>51.82849116990402</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6.002721168061822</v>
+        <v>14.47079488639786</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9561114804066214</v>
+        <v>0.797947078239398</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0933993633204396</v>
+        <v>0.03467934855666</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6788</v>
+        <v>6799</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>407.1276999830501</v>
+        <v>498.8624780082616</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>404.5</v>
+        <v>83.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.04279867012259</v>
+        <v>33.92468413503994</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.12400365238668</v>
+        <v>35.14584135422898</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.212769998305012</v>
+        <v>0.3862478008261624</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.116426663640879</v>
+        <v>-3.050840017132869</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6664</v>
+        <v>6505</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>403.9148626481848</v>
+        <v>498.1418837976925</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>356</v>
+        <v>51.4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>31.72592874722531</v>
+        <v>45.26967278845243</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.97173319595042</v>
+        <v>15.09555790290469</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8914862648184733</v>
+        <v>0.8141883797692429</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-9.396950890332302</v>
+        <v>-0.0203898929277082</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6558</v>
+        <v>6695</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>397.8929421823943</v>
+        <v>493.6855589051152</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>30.15</v>
+        <v>49.55</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>42.41381530634499</v>
+        <v>44.65630930866253</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.54239284482826</v>
+        <v>27.5061105320039</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2892942182394254</v>
+        <v>0.3685558905115098</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3316414611187457</v>
+        <v>-1.293030408336403</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6756</v>
+        <v>6669</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>394.0415417420331</v>
+        <v>489.0981225017883</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>92.7</v>
+        <v>4900</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.93954181928729</v>
+        <v>44.37455752889717</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>32.35615294823437</v>
+        <v>23.9736195352945</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4041541742033085</v>
+        <v>1.409812250178828</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.81834357875087</v>
+        <v>-88.24703809790253</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6589</v>
+        <v>6641</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>386.9257877331081</v>
+        <v>482.4503683995088</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>43.85</v>
+        <v>18.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.3613984481973</v>
+        <v>44.04364715075581</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.04690211554371</v>
+        <v>20.35946943087382</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6925787733108068</v>
+        <v>0.7450368399508801</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4932521969023411</v>
+        <v>-0.0162901610565937</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6781</v>
+        <v>6526</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>383.3952351403107</v>
+        <v>480.5438594775024</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1155</v>
+        <v>618</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.39340432684975</v>
+        <v>43.74676156599664</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.0154613725453</v>
+        <v>20.0086439255318</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.339523514031068</v>
+        <v>0.5543859477502399</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-10.47058926086505</v>
+        <v>-14.22951317717254</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6515</v>
+        <v>6658</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>381.0971200070915</v>
+        <v>479.7527261534617</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>8720</v>
+        <v>175</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.15648553826038</v>
+        <v>46.45694542797317</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>29.37839362152639</v>
+        <v>43.3966911492178</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.109712000709144</v>
+        <v>0.4752726153461691</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-55.18519803395515</v>
+        <v>-7.681879407455714</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6715</v>
+        <v>6546</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>380.9689123473872</v>
+        <v>464.4100027652376</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>371</v>
+        <v>72.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>37.65130350251412</v>
+        <v>45.5026726366231</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.71345848995884</v>
+        <v>22.48761123051281</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5968912347387239</v>
+        <v>0.4410002765237625</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-12.68058740487927</v>
+        <v>-1.10086921659043</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6552</v>
+        <v>6640</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>380.1390524678607</v>
+        <v>457.9918416547387</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>28.95</v>
+        <v>1020</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.86948177026881</v>
+        <v>27.89035279841874</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.93814106570312</v>
+        <v>26.04761513535522</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5139052467860719</v>
+        <v>0.7991841654738696</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.7235273714469785</v>
+        <v>-34.88941847805994</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6640</v>
+        <v>6770</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>367.9918416547387</v>
+        <v>457.6949346584653</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1020</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>27.89035281411297</v>
+        <v>44.40644191746679</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>26.04761517488393</v>
+        <v>26.95629228133082</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7991841654738696</v>
+        <v>0.2694934658465324</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-34.88941847863236</v>
+        <v>-1.978218731545731</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6776</v>
+        <v>6806</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>364.1517430696633</v>
+        <v>447.8946124947396</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>59.5</v>
+        <v>4.48</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.87379047823846</v>
+        <v>32.69275479978509</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.82368096988605</v>
+        <v>30.74197404129084</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.9151743069663322</v>
+        <v>0.2894612494739564</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.096550282910563</v>
+        <v>0.3648987897832407</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6505</v>
+        <v>6761</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>363.092534399882</v>
+        <v>444.9535633100718</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>51.4</v>
+        <v>196</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.26967283605841</v>
+        <v>44.55252291026726</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.09555791355316</v>
+        <v>25.80730700600422</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8092534399882048</v>
+        <v>0.4953563310071801</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0203898930040338</v>
+        <v>-2.015831649287977</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6790</v>
+        <v>6782</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>362.8921230068672</v>
+        <v>441.1781608183457</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>39.7</v>
+        <v>191.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.82849134100955</v>
+        <v>41.80774066573988</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.47079491619924</v>
+        <v>10.79898172013927</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7892123006867139</v>
+        <v>0.6178160818345642</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0346793485375729</v>
+        <v>0.643885656279791</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6805</v>
+        <v>6568</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>359.6917909815648</v>
+        <v>441.0584095209886</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1750</v>
+        <v>175</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.7152560387468</v>
+        <v>34.03975551528471</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.85460663423628</v>
+        <v>24.11283368271792</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4691790981564824</v>
+        <v>0.6058409520988564</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-14.94988807997302</v>
+        <v>-6.054372246419232</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6727</v>
+        <v>6573</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>359.0759930326397</v>
+        <v>440.8781888393706</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>393</v>
+        <v>14.9</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.31727035888572</v>
+        <v>51.50943547729089</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25.34102573155337</v>
+        <v>16.83610662586365</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.90759930326397</v>
+        <v>0.5878188839370584</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-25.93373684666193</v>
+        <v>-0.08899014346706639</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6643</v>
+        <v>6577</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>354.8101795035754</v>
+        <v>439.7283326945856</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>454.5</v>
+        <v>79.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>28.95832889164315</v>
+        <v>49.19314377702237</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>22.38653703677046</v>
+        <v>13.96301380576922</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9810179503575424</v>
+        <v>1.472833269458558</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-17.05882961187631</v>
+        <v>-0.1285729383513772</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6568</v>
+        <v>6706</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>351.0584095209886</v>
+        <v>438.951667781994</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>34.03975553510188</v>
+        <v>42.46024562725148</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>24.11283366455383</v>
+        <v>23.22121029515083</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6058409520988564</v>
+        <v>0.3951667781993964</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-6.054372246476449</v>
+        <v>-6.030018061259677</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6683</v>
+        <v>6582</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>342.8048156179286</v>
+        <v>437.3225282637336</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1390</v>
+        <v>31.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.62565360553724</v>
+        <v>49.01151110279021</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.40658083732653</v>
+        <v>21.75588324451884</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.28048156179286</v>
+        <v>0.7322528263733571</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-41.10442084638893</v>
+        <v>0.0516096301620565</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6532</v>
+        <v>6588</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>338.8712457455184</v>
+        <v>424.1720564081944</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>85.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>37.1813457700753</v>
+        <v>32.42839816738926</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23.09958151087047</v>
+        <v>20.86347003333689</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3871245745518389</v>
+        <v>0.9172056408194332</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.202569115550384</v>
+        <v>-2.01919833735421</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6735</v>
+        <v>6803</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>338.5235298180312</v>
+        <v>422.2866734688745</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>90</v>
+        <v>287.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>37.88395836478208</v>
+        <v>49.41029216420878</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.22756525185825</v>
+        <v>19.79286872442525</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3523529818031238</v>
+        <v>0.7286673468874548</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-2.931516682816845</v>
+        <v>0.1600229433546101</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6806</v>
+        <v>6741</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>337.828919000693</v>
+        <v>415.7035054756322</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>4.48</v>
+        <v>61.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>32.69275484843808</v>
+        <v>40.90647269784628</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>30.7419740347337</v>
+        <v>12.58405683752214</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.282891900069298</v>
+        <v>1.07035054756322</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3648987899931128</v>
+        <v>-0.2061890566363014</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6840</v>
+        <v>6794</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>337.5483901044351</v>
+        <v>413.131453056544</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>65</v>
+        <v>80.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.21958183324768</v>
+        <v>47.28085067825499</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.55685183699486</v>
+        <v>12.98243159192698</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2548390104435097</v>
+        <v>0.8131453056543985</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0209012227866913</v>
+        <v>0.024451237794236</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6679</v>
+        <v>6664</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>336.0474992895136</v>
+        <v>403.9148626481848</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>263.5</v>
+        <v>356</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>36.84087139032535</v>
+        <v>31.72592871912716</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>28.23489387596957</v>
+        <v>21.9717331914673</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6047499289513536</v>
+        <v>0.8914862648184733</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-7.955376534554079</v>
+        <v>-9.396950890332302</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6584</v>
+        <v>6720</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>328.195034400958</v>
+        <v>398.258189951309</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>558</v>
+        <v>148</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.0437676360646</v>
+        <v>38.04591441825441</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.52536513773905</v>
+        <v>29.06477770522199</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8195034400958017</v>
+        <v>0.8258189951308949</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-13.76557571041578</v>
+        <v>0.2392460088129513</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6641</v>
+        <v>6805</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>327.4203147748702</v>
+        <v>385.0108919691898</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18.1</v>
+        <v>1750</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,49 +4792,49 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.04364713851687</v>
+        <v>42.7152560222091</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.35946937944077</v>
+        <v>15.85460665387584</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7420314774870208</v>
+        <v>0.5010891969189777</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0162901611615291</v>
+        <v>-14.94988808235808</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6582</v>
+        <v>6624</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>326.6716027806194</v>
+        <v>382.0555820703859</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>31.2</v>
+        <v>43.45</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.01151132250594</v>
+        <v>50.12241210296812</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.75588328998216</v>
+        <v>13.47584851178916</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6671602780619387</v>
+        <v>0.2055582070385919</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0516096302288297</v>
+        <v>1.33643865764825</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6591</v>
+        <v>6558</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>325.2497004207416</v>
+        <v>367.9259161202685</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>54.4</v>
+        <v>30.15</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>43.07406151044832</v>
+        <v>42.41381520639479</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.58890357722336</v>
+        <v>32.54239284482826</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5249700420741615</v>
+        <v>0.2925916120268533</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0397493157947058</v>
+        <v>-0.331641461137826</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6614</v>
+        <v>6830</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>324.2332417863822</v>
+        <v>363.8696116274676</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>40</v>
+        <v>515</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.46121273687177</v>
+        <v>33.33804150974078</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.8629665320006</v>
+        <v>18.13895604779321</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.923324178638222</v>
+        <v>1.386961162746761</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1419003922778184</v>
+        <v>-24.20316850824652</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6533</v>
+        <v>6725</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>311.1374131138689</v>
+        <v>359.9804498115204</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>196.5</v>
+        <v>273</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>37.94035699285627</v>
+        <v>34.63391021147073</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.81203660381404</v>
+        <v>17.21498108707296</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6137413113868949</v>
+        <v>0.4980449811520424</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-4.158589447921871</v>
+        <v>-5.622900402044377</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6830</v>
+        <v>6727</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>303.3587716841328</v>
+        <v>359.0759930326397</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>515</v>
+        <v>393</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>33.33804151490754</v>
+        <v>37.31727035436328</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.13895603522728</v>
+        <v>25.3410257537814</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.33587716841328</v>
+        <v>0.90759930326397</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-24.20316850834183</v>
+        <v>-25.93373684650929</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6789</v>
+        <v>6643</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>302.8178200603647</v>
+        <v>354.8101795035754</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>455</v>
+        <v>454.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.41380032703813</v>
+        <v>28.95832884686128</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.49909712459638</v>
+        <v>22.38653705071102</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7817820060364672</v>
+        <v>0.9810179503575424</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-13.01329999590235</v>
+        <v>-17.05882961340267</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6577</v>
+        <v>6789</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>299.7283326945856</v>
+        <v>353.1433968530258</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>79.8</v>
+        <v>455</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.19314407833663</v>
+        <v>36.41380031342039</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.96301369105153</v>
+        <v>20.49909711932971</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.472833269458558</v>
+        <v>0.8143396853025738</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1285729383704725</v>
+        <v>-13.01329999590235</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6732</v>
+        <v>6771</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>296.0729278345752</v>
+        <v>352.0745235612022</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>150.5</v>
+        <v>41.85</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>35.02276739371709</v>
+        <v>43.35289521307311</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>25.21363587547087</v>
+        <v>18.65665136561673</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6072927834575189</v>
+        <v>1.207452356120224</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-3.300788750102411</v>
+        <v>0.0882527586515293</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6782</v>
+        <v>6715</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>286.033432546647</v>
+        <v>351.1513318614255</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>191.5</v>
+        <v>371</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,49 +5269,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.80774069514877</v>
+        <v>37.6513034884652</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10.79898167684262</v>
+        <v>24.71345849253721</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6033432546647033</v>
+        <v>0.6151331861425569</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6438856572337501</v>
+        <v>-12.68058740459307</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6725</v>
+        <v>6486</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>284.9804498115204</v>
+        <v>350.4413773387122</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>273</v>
+        <v>81.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.63391024853082</v>
+        <v>39.34004727720428</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.21498106919048</v>
+        <v>20.47451101522752</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4980449811520424</v>
+        <v>0.5441377338712239</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-5.622900402712165</v>
+        <v>0.0756877337309845</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6823</v>
+        <v>6552</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>283.9275954976733</v>
+        <v>350.168107596818</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>65</v>
+        <v>28.95</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>29.50880640888757</v>
+        <v>41.86948173140917</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21.3569788777657</v>
+        <v>19.93814111579866</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8927595497673287</v>
+        <v>0.5168107596818019</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.224084304758067</v>
+        <v>-0.7235273713897384</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6691</v>
+        <v>6754</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>282.1943087544506</v>
+        <v>344.7472165926063</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>637</v>
+        <v>44.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.73465065352687</v>
+        <v>45.65112764702565</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.70234819220921</v>
+        <v>21.64780076428212</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.219430875445064</v>
+        <v>1.47472165926063</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.304443646328124</v>
+        <v>0.0400633422132453</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6645</v>
+        <v>6683</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>278.8723375318287</v>
+        <v>342.8048156179286</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>12.9</v>
+        <v>1390</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>53.62649742698967</v>
+        <v>34.62565359875924</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>31.36262621982826</v>
+        <v>19.40658079558825</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3872337531828725</v>
+        <v>1.28048156179286</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.2049881626014857</v>
+        <v>-41.10442084638893</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6796</v>
+        <v>6532</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>273.1642823702102</v>
+        <v>338.8712457455184</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>57.4</v>
+        <v>85.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>31.73823102343367</v>
+        <v>37.18134574230268</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>32.18796184728904</v>
+        <v>23.09958156657042</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8164282370210234</v>
+        <v>0.3871245745518389</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0481573719291903</v>
+        <v>-2.202569115626698</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6560</v>
+        <v>6735</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>260.4878622856265</v>
+        <v>338.5235298180312</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.92673509452506</v>
+        <v>37.88395835622986</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.56524210356788</v>
+        <v>22.22756522197272</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5487862285626508</v>
+        <v>0.3523529818031238</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1311498374963088</v>
+        <v>-2.931516682778684</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6754</v>
+        <v>6840</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>259.476619535619</v>
+        <v>337.5483901044351</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>44.5</v>
+        <v>65</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.65112777648265</v>
+        <v>47.21958314134117</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.64780074049843</v>
+        <v>19.55685183931353</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.4476619535619</v>
+        <v>0.2548390104435097</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0400633421560057</v>
+        <v>0.0209012227866913</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6739</v>
+        <v>6679</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>258.2749068473583</v>
+        <v>336.0474992895136</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1100</v>
+        <v>263.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.34290468512103</v>
+        <v>36.84087133830686</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.83851444058691</v>
+        <v>28.23489386791124</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8274906847358309</v>
+        <v>0.6047499289513536</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-12.90941282156743</v>
+        <v>-7.955376533886287</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6720</v>
+        <v>6533</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>258.258189951309</v>
+        <v>331.4242195181911</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>148</v>
+        <v>196.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.04591467289558</v>
+        <v>37.94035692936726</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>29.0647776985341</v>
+        <v>21.81203656501394</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8258189951308949</v>
+        <v>0.6424219518191089</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.2392460081451841</v>
+        <v>-4.158589448303474</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6530</v>
+        <v>6584</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>257.2880029385301</v>
+        <v>328.195034400958</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>95</v>
+        <v>558</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>39.44096577892272</v>
+        <v>36.04376762963146</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.55583922045473</v>
+        <v>12.52536519312572</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7288002938530104</v>
+        <v>0.8195034400958017</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,11 +5817,11 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.757599245677114</v>
+        <v>-13.76557571079737</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>256.9551494039215</v>
+        <v>317.1829274539547</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>32.95</v>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>24.34277926475103</v>
+        <v>24.34277918617866</v>
       </c>
       <c r="I102" s="2" t="n">
         <v>15.40007915322712</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2.695514940392153</v>
+        <v>2.718292745395468</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5874,27 +5874,27 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6829</v>
+        <v>6534</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>256.7251133729287</v>
+        <v>313.8616181530596</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>190.5</v>
+        <v>88.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.8737253504781</v>
+        <v>35.46094218010019</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.33730291070461</v>
+        <v>15.76426975267428</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6725113372928647</v>
+        <v>0.3861618153059618</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-4.032968369767664</v>
+        <v>-0.7097000457377743</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6803</v>
+        <v>6753</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>252.2866734688745</v>
+        <v>309.9332954135293</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>287.5</v>
+        <v>119.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.41029214201103</v>
+        <v>37.67070594321424</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.79286866752285</v>
+        <v>12.39021361734378</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7286673468874548</v>
+        <v>0.4933295413529266</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1600229438316067</v>
+        <v>-0.3161865396424881</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6689</v>
+        <v>6722</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>242.7576311528685</v>
+        <v>304.4909294098865</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>66.8</v>
+        <v>38.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.04887427270582</v>
+        <v>47.79014412250937</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.28419966216332</v>
+        <v>16.70611925591253</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7757631152868457</v>
+        <v>0.4490929409886481</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.06369907382713701</v>
+        <v>0.0953738527264658</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6655</v>
+        <v>6732</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>236.3925335208476</v>
+        <v>296.0729278345752</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>120.5</v>
+        <v>150.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>29.24051288661477</v>
+        <v>35.02276732602297</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.15226125815155</v>
+        <v>25.21363593446786</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.639253352084765</v>
+        <v>0.6072927834575189</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.314064434185334</v>
+        <v>-3.300788750293184</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6794</v>
+        <v>6591</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>233.0984863491257</v>
+        <v>295.3219502447433</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>80.7</v>
+        <v>54.4</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.28085076532297</v>
+        <v>43.07406142983836</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.98243145187786</v>
+        <v>22.58890364428107</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8098486349125746</v>
+        <v>0.5321950244743289</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0244512375652805</v>
+        <v>0.0397493158328645</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6692</v>
+        <v>6823</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>218.0877219576036</v>
+        <v>283.9275954976733</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>29.55869829431489</v>
+        <v>29.50880640363182</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>25.89433512850693</v>
+        <v>21.3569788881234</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8087721957603615</v>
+        <v>0.8927595497673287</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0603745187465427</v>
+        <v>-1.224084304863005</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6624</v>
+        <v>6835</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>212.0555820703859</v>
+        <v>277.1494261853395</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>43.45</v>
+        <v>36.25</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.12241210706582</v>
+        <v>38.66875677437494</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.47584851123532</v>
+        <v>10.92580330913414</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.2055582070385919</v>
+        <v>0.2149426185339431</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>1.336438657810426</v>
+        <v>-0.2112829260627546</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6741</v>
+        <v>6655</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>210.7035054756322</v>
+        <v>276.6382027852041</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>61.1</v>
+        <v>120.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.90647276475344</v>
+        <v>29.24051523655247</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.58405681681786</v>
+        <v>13.15226252334748</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.07035054756322</v>
+        <v>0.6638202785204101</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2061890567698589</v>
+        <v>-1.314064458416234</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6486</v>
+        <v>6796</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>210.4413773387122</v>
+        <v>273.430980971821</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>81.2</v>
+        <v>57.4</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.34004741672085</v>
+        <v>31.73823097791228</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.4745110372845</v>
+        <v>32.18796185331469</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5441377338712239</v>
+        <v>0.8430980971821004</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0756877338072975</v>
+        <v>0.0481573722726125</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6680</v>
+        <v>6708</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>205</v>
+        <v>267.7994368176219</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.74217015582834</v>
+        <v>39.75109658596824</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.511360672991678</v>
+        <v>16.12613859135672</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0</v>
+        <v>0.2799436817621889</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,11 +6400,11 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-4.158222881690252</v>
+        <v>-0.2275351921910008</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>182.5652656078209</v>
+        <v>267.7693360972177</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>25.7</v>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>21.57298387450452</v>
+        <v>21.5729839368277</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.22950188289676</v>
+        <v>14.22950192750854</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.256526560782093</v>
+        <v>1.276933609721773</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0337269298854974</v>
+        <v>-0.0337269299045747</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6771</v>
+        <v>6560</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>182.0136259810469</v>
+        <v>260.4878622856265</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>41.85</v>
+        <v>37</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.35289519986354</v>
+        <v>40.92673478009271</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.65665130104379</v>
+        <v>16.56524207224815</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.201362598104692</v>
+        <v>0.5487862285626508</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0882527588232469</v>
+        <v>-0.1311498369048453</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6835</v>
+        <v>6739</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>167.1368748472468</v>
+        <v>258.2749068473583</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>36.25</v>
+        <v>1100</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.66875678705201</v>
+        <v>36.3429046749035</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.92580330913414</v>
+        <v>12.83851444376452</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2136874847246837</v>
+        <v>0.8274906847358309</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2112829258814934</v>
+        <v>-12.90941282118575</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6541</v>
+        <v>6530</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>165.5533834660547</v>
+        <v>257.2880029385301</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>38.4</v>
+        <v>95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>41.69453428408994</v>
+        <v>39.44096576216656</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>18.08391369875109</v>
+        <v>13.555839215822</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.555338346605472</v>
+        <v>0.7288002938530104</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0457148760316809</v>
+        <v>-1.757599245677114</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6722</v>
+        <v>6829</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>164.1249732192427</v>
+        <v>256.7251133729287</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>38.6</v>
+        <v>190.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>47.79014407310685</v>
+        <v>42.87372533710144</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.70611925339196</v>
+        <v>19.33730306109849</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4124973219242748</v>
+        <v>0.6725113372928647</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.095373852850481</v>
+        <v>-4.032968370053864</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6674</v>
+        <v>6689</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>163.1979567188538</v>
+        <v>252.89628175475</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>17.15</v>
+        <v>66.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.32851429846475</v>
+        <v>43.04887409593023</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.52389313475405</v>
+        <v>17.28419967388558</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3197956718853767</v>
+        <v>0.7896281754750011</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0516159476170146</v>
+        <v>0.0636990741896491</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6753</v>
+        <v>6504</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>154.8265024445886</v>
+        <v>229.5628263963266</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>119.5</v>
+        <v>35.45</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>37.6707059760705</v>
+        <v>27.46153218903849</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.39021361249924</v>
+        <v>17.09939778564083</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4826502444588585</v>
+        <v>0.4562826396326628</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.3161865395470902</v>
+        <v>-0.111121427498934</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6534</v>
+        <v>6692</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>153.8385609235098</v>
+        <v>218.0877219576036</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>88.8</v>
+        <v>25</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>35.46094222681954</v>
+        <v>29.55869816928953</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.76426973682214</v>
+        <v>25.89433515620632</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3838560923509776</v>
+        <v>0.8087721957603615</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.7097000457377743</v>
+        <v>-0.0603745186034498</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6708</v>
+        <v>6541</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>152.7994368176219</v>
+        <v>205.6898564685914</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>38.75</v>
+        <v>38.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>39.7511003234971</v>
+        <v>41.69453418083661</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.12613947347078</v>
+        <v>18.08391365977328</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.2799436817621889</v>
+        <v>0.5689856468591421</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.227535199813243</v>
+        <v>0.0457148758981281</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6561</v>
+        <v>6680</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>132.1592157353056</v>
+        <v>205</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>38.99406435399235</v>
+        <v>39.74217014625538</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.10159713644937</v>
+        <v>8.511360669562368</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.215921573530556</v>
+        <v>0</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,11 +6930,11 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-1.877994505223522</v>
+        <v>-4.158222881346823</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>96.4205719478138</v>
+        <v>182.1092342024849</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>24.8</v>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>33.87017963647153</v>
+        <v>33.87017950631197</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.93158707195859</v>
+        <v>12.93158706671864</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.6420571947813809</v>
+        <v>0.7109234202484922</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0283430385211685</v>
+        <v>0.0283430385020915</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6504</v>
+        <v>6674</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>94.5148008069884</v>
+        <v>133.2000545778795</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>35.45</v>
+        <v>17.15</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>27.46153246936898</v>
+        <v>40.32851417308009</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.09939766372439</v>
+        <v>18.52389319247602</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4514800806988395</v>
+        <v>0.3200054577879543</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,11 +7036,64 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1111214276515685</v>
+        <v>-0.0516159475120814</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6561</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>是方</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>132.1592157353056</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>38.99406434391834</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>15.10159713644937</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.215921573530556</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-1.877994505795899</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
